--- a/assetcore/public/import_templates/07_bang_kiem_bao_tri.xlsx
+++ b/assetcore/public/import_templates/07_bang_kiem_bao_tri.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bảng kiểm bảo trì" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ví dụ minh hoạ" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +59,14 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B5E20"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +113,16 @@
         <fgColor rgb="00F8F9FA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE7F6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -133,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -160,6 +177,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -547,7 +579,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📋 HƯỚNG DẪN IMPORT: Bảng kiểm bảo trì  |  MỖI HÀNG = 1 hạng mục kiểm tra, điền từ HÀNG 6 (hàng 5 là ví dụ mẫu). 5 cột đầu (tên mẫu, danh mục, loại bảo trì, phiên bản, ngày hiệu lực) LẶP LẠI y hệt ở mọi hàng cùng một mẫu — hệ thống gộp theo Danh mục + Loại bảo trì. Danh mục điền TÊN, không điền mã.</t>
+          <t>📋 HƯỚNG DẪN IMPORT: Bảng kiểm bảo trì  |  MỖI HÀNG = 1 hạng mục kiểm tra, điền từ HÀNG 6 (hàng 5 là ví dụ mẫu). 5 cột đầu (tên mẫu, danh mục, loại bảo trì, phiên bản, ngày hiệu lực) LẶP LẠI y hệt ở mọi hàng cùng một mẫu — hệ thống gộp theo Danh mục + Loại bảo trì. NHIỀU MẪU trong cùng file: điền tiếp xuống dưới với Danh mục / Loại bảo trì khác — xem sheet 'Ví dụ minh hoạ'. Danh mục điền TÊN, không điền mã.</t>
         </is>
       </c>
     </row>
@@ -745,7 +777,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Máy chẩn đoán hình ảnh</t>
+          <t>Máy thở</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -2204,16 +2236,476 @@
     <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C6:C105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="C6:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Hàng quý,Nửa năm,Hàng năm,Đột xuất"</formula1>
     </dataValidation>
-    <dataValidation sqref="G6:G105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="G6:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"Đạt/Không đạt,Số đo,Ghi chú"</formula1>
     </dataValidation>
-    <dataValidation sqref="K6:K105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
+    <dataValidation sqref="K6:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách." type="list">
       <formula1>"1,0"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>🧭 VÍ DỤ MINH HOẠ — ĐIỀN NHIỀU MẪU BẢNG KIỂM TRONG MỘT FILE  |  Sheet này chỉ để xem, hệ thống KHÔNG nhập dữ liệu ở đây. Chép cách điền sang sheet 'Bảng kiểm bảo trì'. Quy tắc: mỗi hàng = 1 hạng mục; 5 cột đầu lặp lại y hệt ở mọi hàng cùng mẫu; đổi Danh mục hoặc Loại bảo trì = sang mẫu mới. Các hàng cùng mẫu KHÔNG bắt buộc phải liền nhau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Tên mẫu bảng kiểm</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>Danh mục tài sản</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Loại bảo trì định kỳ</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Phiên bản</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Ngày hiệu lực</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Nội dung kiểm tra</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Cách ghi nhận kết quả</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Đơn vị đo</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Ngưỡng dưới</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Ngưỡng trên</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Hạng mục trọng yếu?</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Mục tham chiếu tài liệu</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>MẪU 1 — 3 hàng cùng (Máy thở · Hàng quý) ⇒ hệ thống tạo 1 mẫu bảng kiểm gồm 3 hạng mục, đánh số theo thứ tự hàng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Bảng kiểm bảo trì quý — Máy thở</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Máy thở</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>Hàng quý</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="inlineStr">
+        <is>
+          <t>Kiểm tra áp suất khí nén đầu vào</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>Số đo</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="inlineStr">
+        <is>
+          <t>SM §4.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Bảng kiểm bảo trì quý — Máy thở</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Máy thở</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Hàng quý</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>Vệ sinh / thay bộ lọc khí</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Đạt/Không đạt</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr"/>
+      <c r="I5" s="11" t="inlineStr"/>
+      <c r="J5" s="11" t="inlineStr"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>SM §5.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
+        <is>
+          <t>Bảng kiểm bảo trì quý — Máy thở</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Máy thở</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>Hàng quý</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Đo sai số thể tích khí lưu thông</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>Số đo</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="I6" s="11" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="inlineStr">
+        <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>SM §6.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>MẪU 2 — điền TIẾP XUỐNG DƯỚI, không cần file mới. Khác Danh mục (Máy siêu âm) nên tách thành mẫu thứ hai.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Bảng kiểm bảo trì năm — Máy siêu âm</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Máy siêu âm chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Hàng năm</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Kiểm tra đầu dò: nứt, bong lớp phủ</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Đạt/Không đạt</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>SM §3.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>Bảng kiểm bảo trì năm — Máy siêu âm</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Máy siêu âm chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Hàng năm</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Đo dòng rò vỏ máy</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Số đo</t>
+        </is>
+      </c>
+      <c r="H9" s="13" t="inlineStr">
+        <is>
+          <t>µA</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>IEC 60601</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Bảng kiểm bảo trì năm — Máy siêu âm</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Máy siêu âm chẩn đoán</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Hàng năm</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Kiểm tra chất lượng ảnh bằng phantom</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>QC §2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>➡ KẾT QUẢ: 6 hàng ở trên ⇒ 2 mẫu bảng kiểm (mỗi mẫu 3 hạng mục). Bước xem trước trên màn hình sẽ liệt kê đúng từng mẫu và số hạng mục — đối chiếu trước khi bấm nhập. Mẫu đã có sẵn trong hệ thống: bật 'Cập nhật mẫu đã có' để THAY toàn bộ hạng mục bằng nội dung file (không bật thì các hàng đó bị chặn).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A7:L7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>